--- a/Output.xlsx
+++ b/Output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PBSV\Moudle 1 Workflow\Supabase\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9A54B72E-4650-4C3A-BE65-CC24A701D5E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{808901C5-7E1D-489B-BF93-A5AEFCB5E36E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{4E4D5267-1D24-4D16-81C5-33E5846349ED}"/>
+    <workbookView xWindow="0" yWindow="1455" windowWidth="28800" windowHeight="11280" xr2:uid="{4E4D5267-1D24-4D16-81C5-33E5846349ED}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Số hiệu lệnh</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>Tên Công ty</t>
+  </si>
+  <si>
+    <t>Nhóm khách hàng</t>
+  </si>
+  <si>
+    <t>Phân loại khách hàng</t>
   </si>
 </sst>
 </file>
@@ -461,7 +467,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4FB3940-D4F0-4324-A430-89048640DB88}">
-  <dimension ref="A1:Q1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.140625" customWidth="1"/>
@@ -479,9 +485,10 @@
     <col min="15" max="15" width="16.85546875" customWidth="1"/>
     <col min="16" max="16" width="20" customWidth="1"/>
     <col min="17" max="17" width="13.42578125" customWidth="1"/>
+    <col min="18" max="18" width="17.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>3</v>
       </c>
@@ -532,6 +539,12 @@
       </c>
       <c r="Q1" t="s">
         <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
